--- a/site/exports/hnu-law.xlsx
+++ b/site/exports/hnu-law.xlsx
@@ -792,7 +792,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -853,7 +853,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1337,7 +1337,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1406,7 +1406,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L14" s="2" t="b">
